--- a/assets/csv/staff.xlsx
+++ b/assets/csv/staff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/hassan_491_osu_edu/Documents/Documents/GitHub/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6946CC7C-9354-C643-B5DB-A85F376C618A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{6946CC7C-9354-C643-B5DB-A85F376C618A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{505171A5-5C27-B343-AC0B-B737171D7B57}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>Sl.</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Geography</t>
   </si>
   <si>
-    <t>Ahmed</t>
-  </si>
-  <si>
     <t>Uddin</t>
   </si>
   <si>
@@ -89,12 +86,6 @@
     <t>Uzzal Kumar</t>
   </si>
   <si>
-    <t>Siddik</t>
-  </si>
-  <si>
-    <t>Foeaz</t>
-  </si>
-  <si>
     <t>Tanvir</t>
   </si>
   <si>
@@ -116,9 +107,6 @@
     <t>Dash</t>
   </si>
   <si>
-    <t>Alom</t>
-  </si>
-  <si>
     <t>tanvir.5</t>
   </si>
   <si>
@@ -143,18 +131,9 @@
     <t>dash.52</t>
   </si>
   <si>
-    <t>alom.1</t>
-  </si>
-  <si>
-    <t>ahmed.1352</t>
-  </si>
-  <si>
     <t>Post-Doc</t>
   </si>
   <si>
-    <t>Staff</t>
-  </si>
-  <si>
     <t>Physiology and Cell Biology (Anesthesiology)</t>
   </si>
   <si>
@@ -170,23 +149,17 @@
     <t>chemical and biomolecular engineering</t>
   </si>
   <si>
-    <t>Comprehensive Cancer Center-Wexner Medical Center</t>
-  </si>
-  <si>
     <t>Wexner Medical Center</t>
   </si>
   <si>
     <t>Civil, Environmental and Geodetic Engineering</t>
-  </si>
-  <si>
-    <t>Biochemistry Program (Microbiology)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -226,12 +199,6 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -253,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -271,7 +238,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1650962B-F96C-FE4E-A26E-251242D6E0F9}">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="19.83203125" customWidth="1"/>
@@ -623,46 +589,46 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
       <c r="B3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>3</v>
@@ -671,146 +637,126 @@
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
-      <c r="B10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
-      <c r="B11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>44</v>
-      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3"/>
@@ -1414,35 +1360,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="3"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="3"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="3"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="3"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
